--- a/docs/game/achievements-zh_CN.xlsx
+++ b/docs/game/achievements-zh_CN.xlsx
@@ -61,7 +61,7 @@
     <t>拥有10000贝壳</t>
   </si>
   <si>
-    <t>……钓鱼的概率是完全随机的</t>
+    <t>……钓鱼的概率是完全随机的（隐藏）</t>
   </si>
   <si>
     <t>连续5次钓上同一种鱼</t>
@@ -130,13 +130,13 @@
     <t>闲来无事（隐藏）</t>
   </si>
   <si>
-    <t>戳护眼绿幕中的装饰物累计10000次</t>
+    <t>把玩藏品200次。</t>
   </si>
   <si>
     <t>意外收获（隐藏）</t>
   </si>
   <si>
-    <t>用非常规方式获取7个苹果。（冥想、钓苹果、锄头砍树、在树下吃苹果、在树下吃含有苹果的菜品、向水塘中丢苹果、用逗猫棒吸引）</t>
+    <t>用非常规方式获取7个苹果。（冥想、钓苹果、锄头戳树、在树下吃苹果、在树下吃含有苹果的菜品、向水塘中丢苹果、用逗猫棒吸引）</t>
   </si>
   <si>
     <t>合影（隐藏）</t>
@@ -1085,7 +1085,7 @@
   <dimension ref="A1:B20"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="1"/>
   <cols>
-    <col min="1" max="1" width="27.5454545454545" customWidth="1"/>
+    <col min="1" max="1" width="33.4545454545455" customWidth="1"/>
     <col min="2" max="2" width="94.7272727272727" customWidth="1"/>
   </cols>
   <sheetData>
